--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486933_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486933_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0655</v>
+        <v>5.8744</v>
       </c>
       <c r="E2" t="n">
-        <v>4.888</v>
+        <v>4.6672</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1775</v>
+        <v>1.2072</v>
       </c>
       <c r="G2" t="n">
         <v>1.5805</v>
@@ -610,13 +610,13 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6512</v>
+        <v>0.4601</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8986</v>
+        <v>0.6778</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2474</v>
+        <v>-0.2178</v>
       </c>
       <c r="V2" t="n">
         <v>1.9856</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.607</v>
+        <v>4.1359</v>
       </c>
       <c r="E3" t="n">
-        <v>6.758</v>
+        <v>6.4055</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1511</v>
+        <v>-2.2696</v>
       </c>
       <c r="G3" t="n">
         <v>3.8377</v>
@@ -688,13 +688,13 @@
         <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8005</v>
+        <v>0.3294</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8909</v>
+        <v>0.5384</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.209</v>
       </c>
       <c r="V3" t="n">
         <v>0.5848</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4792</v>
+        <v>3.9091</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8981</v>
+        <v>3.2391</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="G4" t="n">
         <v>5.2888</v>
@@ -766,13 +766,13 @@
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4909</v>
+        <v>-0.061</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1822</v>
+        <v>0.1588</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3087</v>
+        <v>-0.2198</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7027</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7658</v>
+        <v>2.6594</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9344</v>
+        <v>3.7983</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1686</v>
+        <v>-1.1389</v>
       </c>
       <c r="G5" t="n">
         <v>-1.2126</v>
@@ -844,13 +844,13 @@
         <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4877</v>
+        <v>0.4059</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2326</v>
+        <v>0.6314</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2551</v>
+        <v>-0.2255</v>
       </c>
       <c r="V5" t="n">
         <v>3.0554</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8359</v>
+        <v>1.3861</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7205</v>
+        <v>3.2707</v>
       </c>
       <c r="F6" t="n">
         <v>-1.8846</v>
@@ -922,10 +922,10 @@
         <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.0309</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3062</v>
+        <v>0.244</v>
       </c>
       <c r="U6" t="n">
         <v>-0.2749</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6221</v>
+        <v>0.5554</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4745</v>
+        <v>-0.3041</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0966</v>
+        <v>0.8595</v>
       </c>
       <c r="G7" t="n">
         <v>2.6024</v>
@@ -1000,13 +1000,13 @@
         <v>1.4374</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1154</v>
+        <v>-0.1821</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5774</v>
+        <v>-0.4069</v>
       </c>
       <c r="U7" t="n">
-        <v>0.462</v>
+        <v>0.2249</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2222</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4756</v>
+        <v>-0.2228</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5068</v>
+        <v>-0.4022</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0312</v>
+        <v>0.1794</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8688</v>
@@ -1078,13 +1078,13 @@
         <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4282</v>
+        <v>-0.1754</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4534</v>
+        <v>-0.3488</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0252</v>
+        <v>0.1734</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5006</v>
+        <v>-1.6341</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0567</v>
+        <v>1.6267</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.5572</v>
+        <v>-3.2608</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0282</v>
@@ -1156,13 +1156,13 @@
         <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2403</v>
+        <v>-0.3739</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2167</v>
+        <v>-0.2133</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.457</v>
+        <v>-0.1606</v>
       </c>
       <c r="V9" t="n">
         <v>1.7679</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0823</v>
+        <v>-2.8591</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9087</v>
+        <v>-1.8041</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1736</v>
+        <v>-1.0551</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2078</v>
@@ -1234,13 +1234,13 @@
         <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4557</v>
+        <v>-0.2325</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4611</v>
+        <v>-0.3565</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0054</v>
+        <v>0.124</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8295</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1868</v>
+        <v>-4.6859</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9768</v>
+        <v>-2.1201</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2101</v>
+        <v>-2.5658</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7601</v>
@@ -1312,13 +1312,13 @@
         <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2821</v>
+        <v>-0.2169</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0272</v>
+        <v>-0.1706</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3093</v>
+        <v>-0.0464</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2447</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.1302</v>
+        <v>9.118400000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>17.3889</v>
+        <v>18.377</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.258800000000001</v>
+        <v>-9.258699999999999</v>
       </c>
       <c r="G12" t="n">
         <v>5.421399999999998</v>
@@ -1390,13 +1390,13 @@
         <v>12.3206</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0655</v>
+        <v>-0.07729999999999992</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2339000000000003</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8315999999999998</v>
+        <v>-0.8317</v>
       </c>
       <c r="V12" t="n">
         <v>4.8008</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2749</v>
+        <v>6.0549</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7384</v>
+        <v>6.5752</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4635</v>
+        <v>-0.5203</v>
       </c>
       <c r="G13" t="n">
         <v>3.8359</v>
@@ -1468,13 +1468,13 @@
         <v>2.0534</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8547</v>
+        <v>-0.0746</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2438</v>
+        <v>-0.407</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6108</v>
+        <v>0.3324</v>
       </c>
       <c r="V13" t="n">
         <v>0.2402</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8749</v>
+        <v>3.1372</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9338</v>
+        <v>4.5614</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0588</v>
+        <v>-1.4242</v>
       </c>
       <c r="G14" t="n">
         <v>2.9039</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2507</v>
+        <v>0.0116</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7169</v>
+        <v>-0.0892</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.1008</v>
       </c>
       <c r="V14" t="n">
         <v>1.6591</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4278</v>
+        <v>2.6155</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9327</v>
+        <v>4.6756</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5049</v>
+        <v>-2.06</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.462</v>
+        <v>3.7075</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.052</v>
+        <v>3.4968</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.41</v>
+        <v>0.2107</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2631</v>
+        <v>6.1584</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0263</v>
+        <v>4.1851</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2368</v>
+        <v>1.9733</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7251</v>
+        <v>-2.4509</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.6883</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6468</v>
+        <v>-1.7626</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8481</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2204</v>
+        <v>0.524</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6696</v>
+        <v>-0.1707</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5508</v>
+        <v>0.6947</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.1786</v>
+        <v>-0.5893</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7679</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1786</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4039</v>
+        <v>0.0278</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7342</v>
+        <v>0.6774</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3302</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7075</v>
+        <v>-1.462</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4968</v>
+        <v>-0.052</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2107</v>
+        <v>-1.41</v>
       </c>
       <c r="J16" t="n">
-        <v>6.1584</v>
+        <v>0.2631</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1851</v>
+        <v>0.0263</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9733</v>
+        <v>0.2368</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4509</v>
+        <v>-1.7251</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6883</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7626</v>
+        <v>-1.6468</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.0267</v>
+        <v>1.8481</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6876</v>
+        <v>0.8204</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1121</v>
+        <v>0.4144</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4245</v>
+        <v>0.406</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5893</v>
+        <v>-1.1786</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3573</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="17">
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2478</v>
+        <v>-0.1706</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.159</v>
+        <v>-0.5774</v>
       </c>
       <c r="F17" t="n">
         <v>0.4068</v>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.4107</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4997</v>
+        <v>0.0813</v>
       </c>
       <c r="U17" t="n">
         <v>0.3294</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7683</v>
+        <v>-1.2128</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5778</v>
+        <v>0.8455</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.346</v>
+        <v>-2.0583</v>
       </c>
       <c r="G18" t="n">
         <v>-2.789</v>
@@ -1858,13 +1858,13 @@
         <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0906</v>
+        <v>0.646</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2784</v>
+        <v>0.5462</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1879</v>
+        <v>0.0998</v>
       </c>
       <c r="V18" t="n">
         <v>0.1088</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3521</v>
+        <v>-3.175</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9563</v>
+        <v>0.3287</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3084</v>
+        <v>-3.5037</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6364</v>
@@ -1936,13 +1936,13 @@
         <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3111</v>
+        <v>0.4881</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0808</v>
+        <v>0.4532</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2303</v>
+        <v>0.035</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5893</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.7562</v>
+        <v>-4.9194</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4274</v>
+        <v>-2.009</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3287</v>
+        <v>-2.9103</v>
       </c>
       <c r="G20" t="n">
         <v>-5.6148</v>
@@ -2014,13 +2014,13 @@
         <v>2.4641</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0736</v>
+        <v>0.7632</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4729</v>
+        <v>-0.0545</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3993</v>
+        <v>0.8177</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5052</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.483000000000001</v>
+        <v>-7.6984</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.0279</v>
+        <v>-5.8187</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4551</v>
+        <v>-1.8798</v>
       </c>
       <c r="G21" t="n">
         <v>-4.9638</v>
@@ -2092,13 +2092,13 @@
         <v>1.8481</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5192</v>
+        <v>0.2653</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1513</v>
+        <v>0.0579</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.368</v>
+        <v>0.2074</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7679</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.1303</v>
+        <v>-5.340800000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>9.258900000000001</v>
+        <v>9.258699999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-17.3888</v>
+        <v>-14.5995</v>
       </c>
       <c r="G22" t="n">
         <v>-5.421399999999999</v>
@@ -2170,13 +2170,13 @@
         <v>13.3472</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0654</v>
+        <v>3.8547</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8314999999999999</v>
+        <v>0.8316</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2337999999999998</v>
+        <v>3.0232</v>
       </c>
       <c r="V22" t="n">
         <v>-4.8008</v>
